--- a/backend/plantillas/plantilla_asignaturas_ras_il.xlsx
+++ b/backend/plantillas/plantilla_asignaturas_ras_il.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,20 +444,25 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>sede</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>ra_descripcion</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>ra_porcentaje</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>indicador_descripcion</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>indicador_porcentaje</t>
         </is>
@@ -466,172 +471,96 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>MAT201</t>
+          <t>750026C</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Calculo Diferencial</t>
+          <t>DESARROLLO DE APLICACIONES PARA DISPOSITIVOS MOVILES</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DOC001</t>
+          <t>DOC1001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>TDS</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Resuelve problemas con funciones</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Construye aplicaciones moviles funcionales</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
         <v>50</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Identifica tipo de funcion</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>40</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Implementa interfaces responsivas</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MAT201</t>
+          <t>750026C</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Calculo Diferencial</t>
+          <t>DESARROLLO DE APLICACIONES PARA DISPOSITIVOS MOVILES</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DOC001</t>
+          <t>DOC1001</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TDS</t>
+          <t>2724</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>50</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Resuelve problemas con funciones</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Despliega aplicaciones moviles seguras</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
         <v>50</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Aplica derivadas correctamente</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MAT201</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Calculo Diferencial</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DOC001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TDS</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Modela situaciones reales</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>50</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Interpreta resultados del modelo</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MAT201</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Calculo Diferencial</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DOC001</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TDS</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Modela situaciones reales</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>50</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Justifica procedimiento matematico</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Configura seguridad y autenticacion</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
         <v>50</v>
       </c>
     </row>

--- a/backend/plantillas/plantilla_asignaturas_ras_il.xlsx
+++ b/backend/plantillas/plantilla_asignaturas_ras_il.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:L3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,30 +439,40 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>periodo</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>grupo</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>sede</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>creditos</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>ra_descripcion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ra_porcentaje</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>indicador_descripcion</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>indicador_porcentaje</t>
         </is>
@@ -489,30 +499,32 @@
           <t>2724</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
         <is>
           <t>Construye aplicaciones moviles funcionales</t>
         </is>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>50</v>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>Implementa interfaces responsivas</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>50</v>
       </c>
     </row>
@@ -537,30 +549,32 @@
           <t>2724</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
         <is>
           <t>Despliega aplicaciones moviles seguras</t>
         </is>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>50</v>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>Configura seguridad y autenticacion</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>50</v>
       </c>
     </row>
